--- a/docentes/Torres Sánchez José Luis - Estadisticos 20222.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
   </si>
 </sst>
 </file>
@@ -606,16 +624,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,16 +650,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,16 +676,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>58.62</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -717,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>96.77</v>
+        <v>93.55</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -743,16 +770,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>96.77</v>
+        <v>93.55</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -769,16 +796,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>62.07</v>
+        <v>58.62</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -820,16 +847,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920203</v>
+        <v>21330051920207</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -843,16 +870,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920193</v>
+        <v>21330051920209</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -861,6 +888,52 @@
         <v>11</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920190</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20222.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20222.xlsx
@@ -73,40 +73,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RICO</t>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
   </si>
   <si>
     <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920207</v>
+        <v>21330051920209</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920209</v>
+        <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -888,12 +888,12 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920190</v>
+        <v>21330051920192</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920192</v>
+        <v>21330051920207</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20222.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,42 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -744,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>93.55</v>
+        <v>96.77</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -770,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>93.55</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>58.62</v>
+        <v>96.55</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -845,98 +809,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920209</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920190</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920192</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920207</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
